--- a/data/trans_orig/MCS12_SP_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2007</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144484</t>
+          <t>146813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190096</t>
+          <t>189546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85036</t>
+          <t>85827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122303</t>
+          <t>123368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240701</t>
+          <t>241354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299710</t>
+          <t>300549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236523</t>
+          <t>237818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>287750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231897</t>
+          <t>233140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282028</t>
+          <t>282040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485579</t>
+          <t>483228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554919</t>
+          <t>556717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143882</t>
+          <t>146682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>189319</t>
+          <t>188934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167458</t>
+          <t>163328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209867</t>
+          <t>211271</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>320947</t>
+          <t>324897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>385883</t>
+          <t>389203</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80886</t>
+          <t>81721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116774</t>
+          <t>117367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121710</t>
+          <t>120733</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161472</t>
+          <t>160883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212395</t>
+          <t>211225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>269001</t>
+          <t>266665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188239</t>
+          <t>185477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>242999</t>
+          <t>240563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128886</t>
+          <t>128263</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>175084</t>
+          <t>173903</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>328732</t>
+          <t>331238</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>401055</t>
+          <t>400597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>301945</t>
+          <t>303147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>362210</t>
+          <t>366290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>245981</t>
+          <t>243199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>301489</t>
+          <t>301736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>563877</t>
+          <t>565010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>647544</t>
+          <t>647466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>199817</t>
+          <t>201858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253688</t>
+          <t>257330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230516</t>
+          <t>233351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288446</t>
+          <t>290661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>451041</t>
+          <t>447443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>525478</t>
+          <t>527396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161313</t>
+          <t>162044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212824</t>
+          <t>214870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>261193</t>
+          <t>257975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>316764</t>
+          <t>316627</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>435805</t>
+          <t>434096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>514991</t>
+          <t>514339</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159142</t>
+          <t>157942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205602</t>
+          <t>205013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101535</t>
+          <t>101615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140574</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271159</t>
+          <t>269386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332011</t>
+          <t>332438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>175198</t>
+          <t>175487</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>226983</t>
+          <t>225683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>168738</t>
+          <t>167319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>213315</t>
+          <t>214115</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>358396</t>
+          <t>355710</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>425296</t>
+          <t>423552</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155163</t>
+          <t>155063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205003</t>
+          <t>202406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>174419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220571</t>
+          <t>221506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>343551</t>
+          <t>342126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>408272</t>
+          <t>407605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98213</t>
+          <t>98505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140244</t>
+          <t>140617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156002</t>
+          <t>155675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201186</t>
+          <t>199594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265770</t>
+          <t>267051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>325976</t>
+          <t>328531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>189946</t>
+          <t>191432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>239989</t>
+          <t>242599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>143895</t>
+          <t>145416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193100</t>
+          <t>194494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>352519</t>
+          <t>348335</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>421178</t>
+          <t>420611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260576</t>
+          <t>256905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314434</t>
+          <t>312048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261893</t>
+          <t>261904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>319380</t>
+          <t>317412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>536287</t>
+          <t>535327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615266</t>
+          <t>613733</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>208940</t>
+          <t>207474</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>260865</t>
+          <t>261056</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>262007</t>
+          <t>260481</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>320116</t>
+          <t>318425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>485241</t>
+          <t>484301</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>561955</t>
+          <t>560983</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>184794</t>
+          <t>181942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234299</t>
+          <t>230856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>260388</t>
+          <t>263242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320810</t>
+          <t>321584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461419</t>
+          <t>462869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>535194</t>
+          <t>537984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>724972</t>
+          <t>722984</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>827270</t>
+          <t>825487</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>500866</t>
+          <t>497269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>585130</t>
+          <t>587058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1258318</t>
+          <t>1255085</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1382744</t>
+          <t>1380323</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1030978</t>
+          <t>1031605</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1138874</t>
+          <t>1138358</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>947484</t>
+          <t>950043</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1059407</t>
+          <t>1056859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2022030</t>
+          <t>2019315</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2168851</t>
+          <t>2170910</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758238</t>
+          <t>760825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>853392</t>
+          <t>859548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>886066</t>
+          <t>885793</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>985180</t>
+          <t>986774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1671549</t>
+          <t>1666734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1812193</t>
+          <t>1808574</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>567515</t>
+          <t>570263</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>656212</t>
+          <t>662516</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>841377</t>
+          <t>846053</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>950929</t>
+          <t>947894</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1444252</t>
+          <t>1446647</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1579259</t>
+          <t>1569483</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2012</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>176326</t>
+          <t>176949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223367</t>
+          <t>223294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104057</t>
+          <t>103150</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144826</t>
+          <t>144369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>291957</t>
+          <t>292506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>360765</t>
+          <t>353892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132985</t>
+          <t>133157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177515</t>
+          <t>179738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90606</t>
+          <t>91689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131789</t>
+          <t>130186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234943</t>
+          <t>234665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295170</t>
+          <t>292297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>186810</t>
+          <t>182305</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>236379</t>
+          <t>231018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>196686</t>
+          <t>199337</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>248344</t>
+          <t>249062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>397280</t>
+          <t>393461</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>467215</t>
+          <t>467626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120898</t>
+          <t>122107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161462</t>
+          <t>163876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>213046</t>
+          <t>217698</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>266331</t>
+          <t>268319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>344530</t>
+          <t>347490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>414457</t>
+          <t>415488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>251478</t>
+          <t>252002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>312008</t>
+          <t>308521</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210337</t>
+          <t>207801</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>264716</t>
+          <t>265603</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>473869</t>
+          <t>477513</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>557102</t>
+          <t>558564</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>222822</t>
+          <t>223627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>280186</t>
+          <t>277548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>173144</t>
+          <t>169504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223217</t>
+          <t>221075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>409269</t>
+          <t>407986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>486935</t>
+          <t>485535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228450</t>
+          <t>226637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283260</t>
+          <t>282145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245347</t>
+          <t>245138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302039</t>
+          <t>305586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>487301</t>
+          <t>485580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>569119</t>
+          <t>567080</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>206677</t>
+          <t>205571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>264854</t>
+          <t>262282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>296586</t>
+          <t>294166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>357198</t>
+          <t>360001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>521803</t>
+          <t>515618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>601437</t>
+          <t>600736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243794</t>
+          <t>248111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301379</t>
+          <t>305344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192429</t>
+          <t>192051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>244490</t>
+          <t>243461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>453161</t>
+          <t>453044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527588</t>
+          <t>532004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>117573</t>
+          <t>117416</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>162811</t>
+          <t>162807</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82049</t>
+          <t>81117</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120979</t>
+          <t>120041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>210319</t>
+          <t>210308</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>270280</t>
+          <t>269001</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>169654</t>
+          <t>166342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217882</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194339</t>
+          <t>194150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245136</t>
+          <t>246363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371946</t>
+          <t>374290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446942</t>
+          <t>447076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131898</t>
+          <t>132144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178720</t>
+          <t>177530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>215482</t>
+          <t>210912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>270213</t>
+          <t>267218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356324</t>
+          <t>360614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429261</t>
+          <t>434655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>217987</t>
+          <t>217779</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>270208</t>
+          <t>272220</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>169605</t>
+          <t>170188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219684</t>
+          <t>221515</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>399793</t>
+          <t>402967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>478454</t>
+          <t>474342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182126</t>
+          <t>181585</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234202</t>
+          <t>234200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157731</t>
+          <t>155357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206561</t>
+          <t>205253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>352633</t>
+          <t>351244</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>425558</t>
+          <t>422856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>235853</t>
+          <t>236435</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>292335</t>
+          <t>294531</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>292951</t>
+          <t>290901</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>353388</t>
+          <t>353271</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>545714</t>
+          <t>545053</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>628767</t>
+          <t>625522</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>206783</t>
+          <t>208098</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>264183</t>
+          <t>265760</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>324645</t>
+          <t>326112</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>387158</t>
+          <t>390151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>551210</t>
+          <t>554524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>633461</t>
+          <t>639241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>942217</t>
+          <t>945948</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1052199</t>
+          <t>1055951</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>721996</t>
+          <t>721699</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>823443</t>
+          <t>820802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1697734</t>
+          <t>1700898</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1849328</t>
+          <t>1840205</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>699428</t>
+          <t>699332</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>800654</t>
+          <t>799477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>539686</t>
+          <t>541194</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>630683</t>
+          <t>630006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1269645</t>
+          <t>1271848</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1403881</t>
+          <t>1405067</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>867354</t>
+          <t>861039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>971260</t>
+          <t>968249</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>985387</t>
+          <t>987476</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1097453</t>
+          <t>1096698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1879808</t>
+          <t>1882331</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2031518</t>
+          <t>2032240</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>713821</t>
+          <t>712305</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>814262</t>
+          <t>815399</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1105945</t>
+          <t>1102324</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1228193</t>
+          <t>1216963</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1847857</t>
+          <t>1850649</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1995433</t>
+          <t>2004043</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2016</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156706</t>
+          <t>158286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205295</t>
+          <t>203186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128033</t>
+          <t>128391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169172</t>
+          <t>171446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>299192</t>
+          <t>299837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362537</t>
+          <t>360002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142273</t>
+          <t>144745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191310</t>
+          <t>189800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121291</t>
+          <t>121323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163982</t>
+          <t>165674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281360</t>
+          <t>278815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344805</t>
+          <t>342354</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179989</t>
+          <t>183008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>229177</t>
+          <t>231976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>174295</t>
+          <t>173163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>221184</t>
+          <t>220950</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>369015</t>
+          <t>371949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>434902</t>
+          <t>440515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101565</t>
+          <t>102638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143951</t>
+          <t>144688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161938</t>
+          <t>164200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205559</t>
+          <t>208741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>278600</t>
+          <t>279246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>340000</t>
+          <t>339219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>247924</t>
+          <t>248975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>307934</t>
+          <t>305710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221726</t>
+          <t>222286</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279052</t>
+          <t>277866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>485395</t>
+          <t>480113</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>566460</t>
+          <t>562106</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>243156</t>
+          <t>239501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>297300</t>
+          <t>299180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202852</t>
+          <t>203400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259318</t>
+          <t>257089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462433</t>
+          <t>461180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>537529</t>
+          <t>540167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280985</t>
+          <t>279366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338616</t>
+          <t>340353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273406</t>
+          <t>276991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335181</t>
+          <t>335501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>578121</t>
+          <t>570919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658827</t>
+          <t>655120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144924</t>
+          <t>145941</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>192213</t>
+          <t>193481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228598</t>
+          <t>231262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>288512</t>
+          <t>288698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>389270</t>
+          <t>391101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>463088</t>
+          <t>465286</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246035</t>
+          <t>246478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299685</t>
+          <t>297670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227642</t>
+          <t>231045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283938</t>
+          <t>281978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>486935</t>
+          <t>486601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>565613</t>
+          <t>563241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>140813</t>
+          <t>140367</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>187908</t>
+          <t>187592</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125745</t>
+          <t>125134</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>169953</t>
+          <t>170395</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>280277</t>
+          <t>276634</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>345523</t>
+          <t>342400</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159018</t>
+          <t>159303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207532</t>
+          <t>208807</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149553</t>
+          <t>155193</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198436</t>
+          <t>201844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320333</t>
+          <t>322800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390515</t>
+          <t>391985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119533</t>
+          <t>122814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165223</t>
+          <t>163750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184753</t>
+          <t>184232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237107</t>
+          <t>235635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315543</t>
+          <t>316456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382078</t>
+          <t>387062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205566</t>
+          <t>205522</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>258092</t>
+          <t>260507</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196124</t>
+          <t>195047</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>250227</t>
+          <t>248806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>417135</t>
+          <t>415978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>492332</t>
+          <t>495132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176022</t>
+          <t>176784</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225717</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>182301</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>232094</t>
+          <t>235936</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371704</t>
+          <t>367982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441838</t>
+          <t>443459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>271060</t>
+          <t>271069</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>324138</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>288699</t>
+          <t>290409</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>350932</t>
+          <t>347453</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>573019</t>
+          <t>575628</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>662957</t>
+          <t>656908</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180899</t>
+          <t>186093</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>233408</t>
+          <t>235833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>268186</t>
+          <t>269519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>329046</t>
+          <t>329475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>468060</t>
+          <t>466491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>548073</t>
+          <t>546137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>903081</t>
+          <t>898673</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1010172</t>
+          <t>1013042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>821865</t>
+          <t>824233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>927754</t>
+          <t>929767</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1758973</t>
+          <t>1757718</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1907630</t>
+          <t>1907115</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>752313</t>
+          <t>753910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>850446</t>
+          <t>850943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>677208</t>
+          <t>678543</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>781297</t>
+          <t>776108</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1460257</t>
+          <t>1457332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1599068</t>
+          <t>1593249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>945529</t>
+          <t>936464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1049816</t>
+          <t>1048964</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>939707</t>
+          <t>937139</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1047011</t>
+          <t>1050228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1921037</t>
+          <t>1912662</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2070856</t>
+          <t>2060504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>593816</t>
+          <t>597445</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>685543</t>
+          <t>688115</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>898089</t>
+          <t>897801</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1003188</t>
+          <t>1007196</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1519999</t>
+          <t>1521629</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1660006</t>
+          <t>1663316</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2023</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197267</t>
+          <t>200240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254212</t>
+          <t>253363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190614</t>
+          <t>191738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>231692</t>
+          <t>230061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>401778</t>
+          <t>405177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>473635</t>
+          <t>473997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138988</t>
+          <t>138160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189007</t>
+          <t>183673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126310</t>
+          <t>127978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161770</t>
+          <t>161841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276463</t>
+          <t>278136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>334074</t>
+          <t>334269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95540</t>
+          <t>95119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136765</t>
+          <t>136319</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130322</t>
+          <t>131113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>163593</t>
+          <t>162718</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>233818</t>
+          <t>236034</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>287497</t>
+          <t>287096</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109777</t>
+          <t>110349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147604</t>
+          <t>150379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>151802</t>
+          <t>151758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184939</t>
+          <t>185270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>270649</t>
+          <t>271349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322589</t>
+          <t>325875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166856</t>
+          <t>166985</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>412702</t>
+          <t>413493</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>237567</t>
+          <t>237689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>287416</t>
+          <t>286525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>377270</t>
+          <t>375879</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>667021</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285445</t>
+          <t>284863</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>814884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205920</t>
+          <t>204047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251162</t>
+          <t>247934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>509049</t>
+          <t>506797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1178544</t>
+          <t>1209934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -10754,17 +10754,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>220864</t>
+          <t>220865</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119349</t>
+          <t>114906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293840</t>
+          <t>289114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177251</t>
+          <t>176532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220186</t>
+          <t>217950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282240</t>
+          <t>265217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>486214</t>
+          <t>487166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87717</t>
+          <t>86742</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>224176</t>
+          <t>223149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241704</t>
+          <t>243212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>290744</t>
+          <t>289148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>282356</t>
+          <t>278593</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>503763</t>
+          <t>510583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200178</t>
+          <t>200763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258019</t>
+          <t>257968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107104</t>
+          <t>103662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290337</t>
+          <t>300051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285147</t>
+          <t>274288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>522234</t>
+          <t>527704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>162812</t>
+          <t>164678</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>217937</t>
+          <t>218545</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87466</t>
+          <t>90303</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>222749</t>
+          <t>224228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>233334</t>
+          <t>221352</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>424908</t>
+          <t>423535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109769</t>
+          <t>109879</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160241</t>
+          <t>157373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87715</t>
+          <t>83589</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>225549</t>
+          <t>222607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198986</t>
+          <t>189900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>357848</t>
+          <t>356647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128735</t>
+          <t>129644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178063</t>
+          <t>178209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224558</t>
+          <t>224402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635205</t>
+          <t>647226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371187</t>
+          <t>370684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>920798</t>
+          <t>925739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>261601</t>
+          <t>264599</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>325311</t>
+          <t>325566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>201594</t>
+          <t>203806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278203</t>
+          <t>280720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>485053</t>
+          <t>477900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>588269</t>
+          <t>589837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>193543</t>
+          <t>190973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251362</t>
+          <t>249234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170434</t>
+          <t>169690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240641</t>
+          <t>239408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>383952</t>
+          <t>378275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>473483</t>
+          <t>475511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>200592</t>
+          <t>199571</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>258785</t>
+          <t>255688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>264797</t>
+          <t>264123</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>474347</t>
+          <t>478715</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>488633</t>
+          <t>488704</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>736506</t>
+          <t>723345</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159166</t>
+          <t>158321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207619</t>
+          <t>206866</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>237917</t>
+          <t>233498</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>335094</t>
+          <t>335663</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>420322</t>
+          <t>429609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>525171</t>
+          <t>526034</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>822134</t>
+          <t>843461</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1169733</t>
+          <t>1159612</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>778990</t>
+          <t>754451</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1024103</t>
+          <t>1024285</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1752301</t>
+          <t>1750604</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2161995</t>
+          <t>2147228</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>853620</t>
+          <t>848790</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1707185</t>
+          <t>1562704</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>625497</t>
+          <t>616767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>825369</t>
+          <t>820225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1558032</t>
+          <t>1554826</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2377754</t>
+          <t>2487484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>530928</t>
+          <t>556079</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>769761</t>
+          <t>774090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>705442</t>
+          <t>710740</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>988335</t>
+          <t>1009653</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1353087</t>
+          <t>1338490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1703142</t>
+          <t>1693397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>485466</t>
+          <t>501790</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>699541</t>
+          <t>702537</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>953102</t>
+          <t>954129</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1577346</t>
+          <t>1594929</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1551484</t>
+          <t>1545530</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2271052</t>
+          <t>2324808</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146813</t>
+          <t>143458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>189546</t>
+          <t>188122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85827</t>
+          <t>84738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123368</t>
+          <t>121529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>241354</t>
+          <t>241483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>300549</t>
+          <t>297005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237818</t>
+          <t>238637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287750</t>
+          <t>289689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233140</t>
+          <t>234081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282040</t>
+          <t>282695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>483228</t>
+          <t>485743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556717</t>
+          <t>557867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146682</t>
+          <t>145173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>188934</t>
+          <t>190130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>163328</t>
+          <t>165210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>211271</t>
+          <t>210735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>324897</t>
+          <t>319943</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>389203</t>
+          <t>386055</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81721</t>
+          <t>80230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117367</t>
+          <t>115774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120733</t>
+          <t>119959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160883</t>
+          <t>161597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>211225</t>
+          <t>213572</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266665</t>
+          <t>266499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185477</t>
+          <t>188531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>240563</t>
+          <t>242113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128263</t>
+          <t>125975</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173903</t>
+          <t>172923</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>331238</t>
+          <t>330969</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>400597</t>
+          <t>402202</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>303147</t>
+          <t>304878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366290</t>
+          <t>364799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>243199</t>
+          <t>244308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>301736</t>
+          <t>301238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565010</t>
+          <t>562706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>647466</t>
+          <t>647410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201858</t>
+          <t>200893</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257330</t>
+          <t>252779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233351</t>
+          <t>233438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>290661</t>
+          <t>288529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447443</t>
+          <t>449338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>527396</t>
+          <t>527075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162044</t>
+          <t>165084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>214870</t>
+          <t>214366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257975</t>
+          <t>258657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>316627</t>
+          <t>316525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>434096</t>
+          <t>434577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>514339</t>
+          <t>509569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157942</t>
+          <t>156243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205013</t>
+          <t>204282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101615</t>
+          <t>100519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139328</t>
+          <t>141029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>269386</t>
+          <t>271970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332438</t>
+          <t>331701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>175487</t>
+          <t>179097</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>225683</t>
+          <t>225766</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>167319</t>
+          <t>168519</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>214115</t>
+          <t>213694</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>355710</t>
+          <t>359530</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>423552</t>
+          <t>425421</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155063</t>
+          <t>156289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202406</t>
+          <t>202248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174419</t>
+          <t>173665</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221506</t>
+          <t>218900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342126</t>
+          <t>341085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>407605</t>
+          <t>407751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98505</t>
+          <t>98917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140617</t>
+          <t>139561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155675</t>
+          <t>156309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199594</t>
+          <t>202198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267051</t>
+          <t>267801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328531</t>
+          <t>333227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191432</t>
+          <t>192700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>242599</t>
+          <t>240351</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145416</t>
+          <t>146523</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194494</t>
+          <t>193069</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>348335</t>
+          <t>352207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>420611</t>
+          <t>422935</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256905</t>
+          <t>259118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312048</t>
+          <t>312903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261904</t>
+          <t>259399</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317412</t>
+          <t>317704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535327</t>
+          <t>533675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613733</t>
+          <t>619516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>207474</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>261056</t>
+          <t>260672</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>260481</t>
+          <t>260946</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>318425</t>
+          <t>319873</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>484301</t>
+          <t>487176</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>560983</t>
+          <t>562605</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181942</t>
+          <t>181851</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>230856</t>
+          <t>232865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>263242</t>
+          <t>263091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>321584</t>
+          <t>319190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>462869</t>
+          <t>458623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>537984</t>
+          <t>538923</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>722984</t>
+          <t>729715</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>825487</t>
+          <t>826753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>497269</t>
+          <t>498058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>587058</t>
+          <t>587192</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1255085</t>
+          <t>1252318</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1380323</t>
+          <t>1386048</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1031605</t>
+          <t>1033645</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1138358</t>
+          <t>1142457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>950043</t>
+          <t>952975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1056859</t>
+          <t>1059480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2019315</t>
+          <t>2010344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2170910</t>
+          <t>2170799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760825</t>
+          <t>755048</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>859548</t>
+          <t>850736</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>885793</t>
+          <t>879737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>986774</t>
+          <t>992152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1666734</t>
+          <t>1665563</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1808574</t>
+          <t>1815606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>570263</t>
+          <t>566182</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>662516</t>
+          <t>653942</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>846053</t>
+          <t>846234</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>947894</t>
+          <t>944763</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1446647</t>
+          <t>1441934</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1569483</t>
+          <t>1573020</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>176949</t>
+          <t>175204</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223294</t>
+          <t>224109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103150</t>
+          <t>104254</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144369</t>
+          <t>146371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292506</t>
+          <t>292941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>353892</t>
+          <t>355967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133157</t>
+          <t>130866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179738</t>
+          <t>177721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91689</t>
+          <t>91384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130186</t>
+          <t>127531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234665</t>
+          <t>234627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>292297</t>
+          <t>295670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>182305</t>
+          <t>185701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>231018</t>
+          <t>233423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>199337</t>
+          <t>198375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>249062</t>
+          <t>250940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>393461</t>
+          <t>396712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>467626</t>
+          <t>467537</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122107</t>
+          <t>119905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>163876</t>
+          <t>162867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>217698</t>
+          <t>213421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>268319</t>
+          <t>265532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>347490</t>
+          <t>344332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>415488</t>
+          <t>413324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>252002</t>
+          <t>251224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>308521</t>
+          <t>310698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207801</t>
+          <t>209480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>265603</t>
+          <t>264428</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>477513</t>
+          <t>478810</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>558564</t>
+          <t>562498</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>223627</t>
+          <t>222269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>277548</t>
+          <t>281174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169504</t>
+          <t>170426</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221075</t>
+          <t>223221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>407986</t>
+          <t>410161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>485535</t>
+          <t>486231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226637</t>
+          <t>228502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282145</t>
+          <t>289360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245138</t>
+          <t>245525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305586</t>
+          <t>303538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>485580</t>
+          <t>489916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>567080</t>
+          <t>568702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205571</t>
+          <t>205031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>262282</t>
+          <t>262121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>294166</t>
+          <t>297078</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>360001</t>
+          <t>359442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>515618</t>
+          <t>517057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>600736</t>
+          <t>603952</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248111</t>
+          <t>248350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305344</t>
+          <t>301925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192051</t>
+          <t>193046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>243461</t>
+          <t>246222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>453044</t>
+          <t>453814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>532004</t>
+          <t>528855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>117416</t>
+          <t>118711</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>162807</t>
+          <t>164360</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81117</t>
+          <t>82370</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120041</t>
+          <t>122306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>210308</t>
+          <t>210703</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>269001</t>
+          <t>272491</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166342</t>
+          <t>165176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218636</t>
+          <t>216798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194150</t>
+          <t>192847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>246363</t>
+          <t>247487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>374290</t>
+          <t>375754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>447076</t>
+          <t>449156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>130459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177530</t>
+          <t>179835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,82 +5302,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>240560</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>213147</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>265729</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>27,43%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>34,19%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>394716</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>359614</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>430909</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>25,72%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>23,43%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>240560</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>210912</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>267218</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,95%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>27,14%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>34,38%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>394716</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>360614</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>434655</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>25,72%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>217779</t>
+          <t>216157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>272220</t>
+          <t>271619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>170188</t>
+          <t>169742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>221515</t>
+          <t>220540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>402967</t>
+          <t>401989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>474342</t>
+          <t>479717</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181585</t>
+          <t>181749</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234200</t>
+          <t>231440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155357</t>
+          <t>157326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205253</t>
+          <t>206725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351244</t>
+          <t>352374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422856</t>
+          <t>422114</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>236435</t>
+          <t>234457</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>294531</t>
+          <t>290427</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>290901</t>
+          <t>293234</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>353271</t>
+          <t>354099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>545053</t>
+          <t>543066</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>625522</t>
+          <t>624170</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208098</t>
+          <t>209392</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>265760</t>
+          <t>261441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>326112</t>
+          <t>326280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>390151</t>
+          <t>386795</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>554524</t>
+          <t>554036</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>639241</t>
+          <t>634917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>945948</t>
+          <t>940496</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1055951</t>
+          <t>1056795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>721699</t>
+          <t>720834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>820802</t>
+          <t>823426</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1700898</t>
+          <t>1701297</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1840205</t>
+          <t>1846578</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>699332</t>
+          <t>703225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>799477</t>
+          <t>800258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>541194</t>
+          <t>542798</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>630006</t>
+          <t>639352</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1271848</t>
+          <t>1271730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1405067</t>
+          <t>1403144</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>861039</t>
+          <t>860972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>968249</t>
+          <t>969944</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>987476</t>
+          <t>987253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1096698</t>
+          <t>1096516</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1882331</t>
+          <t>1880003</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2032240</t>
+          <t>2033023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>712305</t>
+          <t>718045</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>815399</t>
+          <t>817517</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1102324</t>
+          <t>1104449</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1216963</t>
+          <t>1223517</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1850649</t>
+          <t>1852183</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2004043</t>
+          <t>2000238</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158286</t>
+          <t>160715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203186</t>
+          <t>206156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128391</t>
+          <t>129752</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171446</t>
+          <t>171910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>299837</t>
+          <t>295574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>360002</t>
+          <t>358409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144745</t>
+          <t>142441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189800</t>
+          <t>189582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121323</t>
+          <t>123054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165674</t>
+          <t>165906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278815</t>
+          <t>280411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>342354</t>
+          <t>342460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183008</t>
+          <t>180065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>231976</t>
+          <t>228272</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>173163</t>
+          <t>175369</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>220950</t>
+          <t>221625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>371949</t>
+          <t>368532</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>440515</t>
+          <t>433257</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102638</t>
+          <t>104214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144688</t>
+          <t>143510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164200</t>
+          <t>161947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208741</t>
+          <t>210018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279246</t>
+          <t>276692</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>339219</t>
+          <t>338794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>248975</t>
+          <t>248382</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>305710</t>
+          <t>310191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>222286</t>
+          <t>221189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277866</t>
+          <t>280553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>480113</t>
+          <t>486250</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>562106</t>
+          <t>566291</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239501</t>
+          <t>239279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>299180</t>
+          <t>298167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203400</t>
+          <t>203779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>257089</t>
+          <t>258845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>461180</t>
+          <t>463087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>540167</t>
+          <t>543361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279366</t>
+          <t>279846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340353</t>
+          <t>342663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276991</t>
+          <t>274941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335501</t>
+          <t>335259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>570919</t>
+          <t>573594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655120</t>
+          <t>654978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145941</t>
+          <t>141534</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>193481</t>
+          <t>190881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>231262</t>
+          <t>231823</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>288698</t>
+          <t>287443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>391101</t>
+          <t>390243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>465286</t>
+          <t>465006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246478</t>
+          <t>246226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297670</t>
+          <t>299336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231045</t>
+          <t>228016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>281978</t>
+          <t>281679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>486601</t>
+          <t>487597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563241</t>
+          <t>564335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>140367</t>
+          <t>142065</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>187592</t>
+          <t>187523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125134</t>
+          <t>126410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>170395</t>
+          <t>169482</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>276634</t>
+          <t>280799</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>342400</t>
+          <t>344902</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159303</t>
+          <t>159346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208807</t>
+          <t>207864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155193</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201844</t>
+          <t>198325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322800</t>
+          <t>325442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>391985</t>
+          <t>390937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122814</t>
+          <t>122226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163750</t>
+          <t>167195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184232</t>
+          <t>183383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>235635</t>
+          <t>233081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316456</t>
+          <t>319628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387062</t>
+          <t>384847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205522</t>
+          <t>201939</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>260507</t>
+          <t>258342</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>195047</t>
+          <t>195554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>248806</t>
+          <t>250409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>415978</t>
+          <t>417255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>495132</t>
+          <t>489635</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176784</t>
+          <t>175809</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225137</t>
+          <t>224798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>182301</t>
+          <t>181480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235936</t>
+          <t>235187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367982</t>
+          <t>372497</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443459</t>
+          <t>445930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>271069</t>
+          <t>270620</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>324545</t>
+          <t>326313</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>290409</t>
+          <t>288874</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>347453</t>
+          <t>351259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>575628</t>
+          <t>573843</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>656908</t>
+          <t>654428</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186093</t>
+          <t>185133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235833</t>
+          <t>236637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>269519</t>
+          <t>268487</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>329475</t>
+          <t>325196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>466491</t>
+          <t>467984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>546137</t>
+          <t>545059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>898673</t>
+          <t>908435</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1013042</t>
+          <t>1013294</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>824233</t>
+          <t>819949</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>929767</t>
+          <t>925898</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1757718</t>
+          <t>1762441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1907115</t>
+          <t>1912906</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>753910</t>
+          <t>749263</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>850943</t>
+          <t>853954</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>678543</t>
+          <t>679689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>776108</t>
+          <t>777492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1457332</t>
+          <t>1454200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1593249</t>
+          <t>1598621</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>936464</t>
+          <t>938700</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1048964</t>
+          <t>1044272</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>937139</t>
+          <t>937142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1050228</t>
+          <t>1044897</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1912662</t>
+          <t>1908897</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2060504</t>
+          <t>2067882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>597445</t>
+          <t>597700</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>688115</t>
+          <t>686474</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>897801</t>
+          <t>896862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1007196</t>
+          <t>1007054</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1521629</t>
+          <t>1521531</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1663316</t>
+          <t>1665479</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>225813</t>
+          <t>245585</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200240</t>
+          <t>218577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253363</t>
+          <t>273180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>211205</t>
+          <t>230934</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191738</t>
+          <t>209454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230061</t>
+          <t>255417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>437017</t>
+          <t>476518</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>405177</t>
+          <t>440508</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>473997</t>
+          <t>511404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>160768</t>
+          <t>175256</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138160</t>
+          <t>152216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183673</t>
+          <t>199858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>144198</t>
+          <t>154995</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127978</t>
+          <t>137621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161841</t>
+          <t>174468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>304965</t>
+          <t>330251</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278136</t>
+          <t>299552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>334269</t>
+          <t>362903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>115182</t>
+          <t>123333</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95119</t>
+          <t>102895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136319</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>146251</t>
+          <t>159015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131113</t>
+          <t>141085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>162718</t>
+          <t>177499</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>261434</t>
+          <t>282347</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236034</t>
+          <t>257614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>287096</t>
+          <t>311471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>128401</t>
+          <t>140598</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110349</t>
+          <t>121852</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150379</t>
+          <t>165682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>168207</t>
+          <t>182088</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>151758</t>
+          <t>163597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185270</t>
+          <t>202379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>296608</t>
+          <t>322686</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271349</t>
+          <t>294822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325875</t>
+          <t>350837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>317908</t>
+          <t>348600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166985</t>
+          <t>314814</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>413493</t>
+          <t>388117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>261550</t>
+          <t>283808</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>237689</t>
+          <t>258505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>286525</t>
+          <t>312501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>579458</t>
+          <t>632408</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>375879</t>
+          <t>586052</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>674183</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>478901</t>
+          <t>258249</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>284863</t>
+          <t>228298</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>814884</t>
+          <t>291320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>227128</t>
+          <t>258110</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204047</t>
+          <t>230091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247934</t>
+          <t>283270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>706029</t>
+          <t>516359</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>506797</t>
+          <t>476690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1209934</t>
+          <t>558486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>220865</t>
+          <t>254448</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114906</t>
+          <t>221538</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289114</t>
+          <t>286597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>197911</t>
+          <t>224614</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176532</t>
+          <t>202240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217950</t>
+          <t>248946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>418776</t>
+          <t>479062</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265217</t>
+          <t>441490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>487166</t>
+          <t>520218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170639</t>
+          <t>182534</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86742</t>
+          <t>158905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>223149</t>
+          <t>211031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>266250</t>
+          <t>298579</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>243212</t>
+          <t>274544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>289148</t>
+          <t>323116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>436889</t>
+          <t>481113</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278593</t>
+          <t>447205</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>510583</t>
+          <t>516631</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>227919</t>
+          <t>250149</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200763</t>
+          <t>218363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257968</t>
+          <t>279512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>210742</t>
+          <t>205065</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103662</t>
+          <t>183294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300051</t>
+          <t>230605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>22,62%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>438660</t>
+          <t>455214</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274288</t>
+          <t>418633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527704</t>
+          <t>497209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>189432</t>
+          <t>228330</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>164678</t>
+          <t>199336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>218545</t>
+          <t>260465</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166238</t>
+          <t>196757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90303</t>
+          <t>174080</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>224228</t>
+          <t>218640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>355670</t>
+          <t>425087</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>221352</t>
+          <t>388022</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>423535</t>
+          <t>464374</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>133010</t>
+          <t>154513</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109879</t>
+          <t>129722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157373</t>
+          <t>181080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>165553</t>
+          <t>188031</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83589</t>
+          <t>166202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>222607</t>
+          <t>211854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>298563</t>
+          <t>342545</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>189900</t>
+          <t>307886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356647</t>
+          <t>378503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>151966</t>
+          <t>167353</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129644</t>
+          <t>142922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178209</t>
+          <t>193238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>389098</t>
+          <t>220550</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224402</t>
+          <t>198244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>647226</t>
+          <t>243301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>541063</t>
+          <t>387903</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370684</t>
+          <t>352740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>925739</t>
+          <t>423766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>291191</t>
+          <t>298864</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>264599</t>
+          <t>269494</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>325566</t>
+          <t>330619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>250333</t>
+          <t>271097</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203806</t>
+          <t>246230</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280720</t>
+          <t>300696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>541524</t>
+          <t>569961</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>477900</t>
+          <t>532138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>589837</t>
+          <t>615629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>221236</t>
+          <t>239088</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190973</t>
+          <t>212096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249234</t>
+          <t>270173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>211780</t>
+          <t>228674</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169690</t>
+          <t>204372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239408</t>
+          <t>254330</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>433017</t>
+          <t>467762</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>378275</t>
+          <t>430251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>475511</t>
+          <t>504978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>229244</t>
+          <t>247677</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199571</t>
+          <t>221035</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>255688</t>
+          <t>278694</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>324491</t>
+          <t>282710</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>264123</t>
+          <t>257821</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>478715</t>
+          <t>309134</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>553736</t>
+          <t>530387</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>488704</t>
+          <t>495124</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>723345</t>
+          <t>574477</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>181237</t>
+          <t>200526</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158321</t>
+          <t>177246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206866</t>
+          <t>224992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>302668</t>
+          <t>330601</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>233498</t>
+          <t>306168</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>335663</t>
+          <t>359170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>483905</t>
+          <t>531127</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>429609</t>
+          <t>492231</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>526034</t>
+          <t>567834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1062830</t>
+          <t>1143198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>843461</t>
+          <t>1087760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1159612</t>
+          <t>1209489</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>933830</t>
+          <t>990904</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>754451</t>
+          <t>941103</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1024285</t>
+          <t>1041381</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1996660</t>
+          <t>2134102</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1750604</t>
+          <t>2053094</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2147228</t>
+          <t>2216188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1050337</t>
+          <t>900923</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>848790</t>
+          <t>841929</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1562704</t>
+          <t>954602</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>749344</t>
+          <t>838536</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>616767</t>
+          <t>795255</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>820225</t>
+          <t>881915</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1799681</t>
+          <t>1739459</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1554826</t>
+          <t>1673824</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2487484</t>
+          <t>1813594</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>698301</t>
+          <t>779971</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>556079</t>
+          <t>726144</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774090</t>
+          <t>836812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>834207</t>
+          <t>854370</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>710740</t>
+          <t>811015</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1009653</t>
+          <t>901192</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1532508</t>
+          <t>1634341</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1338490</t>
+          <t>1571172</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1693397</t>
+          <t>1701860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>632243</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>501790</t>
+          <t>636369</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>702537</t>
+          <t>741552</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1126222</t>
+          <t>1031818</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>954129</t>
+          <t>984640</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1594929</t>
+          <t>1076591</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1758466</t>
+          <t>1722829</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1545530</t>
+          <t>1658876</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2324808</t>
+          <t>1792341</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
